--- a/Quasar Members.xlsx
+++ b/Quasar Members.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="146">
   <si>
     <t xml:space="preserve">Name </t>
   </si>
@@ -106,213 +106,213 @@
     <t>rob.wittenmyer@unisq.edu.au</t>
   </si>
   <si>
+    <t>Duncan Wright</t>
+  </si>
+  <si>
+    <t>Duncan.Wright@unisq.edu.au</t>
+  </si>
+  <si>
+    <t>George Zhou</t>
+  </si>
+  <si>
+    <t>Associate Professor</t>
+  </si>
+  <si>
+    <t>george.zhou@unisq.edu.au</t>
+  </si>
+  <si>
+    <t>https://georgezhouastro.wordpress.com/</t>
+  </si>
+  <si>
+    <t>Chelsea Huang</t>
+  </si>
+  <si>
+    <t>chelsea.huang@unisq.edu.au</t>
+  </si>
+  <si>
+    <t>https://chelseahuangexoplanets.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simon Murphy </t>
+  </si>
+  <si>
+    <t>Springfield</t>
+  </si>
+  <si>
+    <t>Stars</t>
+  </si>
+  <si>
+    <t>Simon.Murphy@unisq.edu.au</t>
+  </si>
+  <si>
+    <t>https://simonjmurphy.github.io/</t>
+  </si>
+  <si>
+    <t>Holger Baumgardt</t>
+  </si>
+  <si>
+    <t>h.baumgardt@uq.edu.au</t>
+  </si>
+  <si>
+    <t>https://people.smp.uq.edu.au/HolgerBaumgardt/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Cowley </t>
+  </si>
+  <si>
+    <t>QUT</t>
+  </si>
+  <si>
+    <t>Senior Lecturer</t>
+  </si>
+  <si>
+    <t>Galaxies</t>
+  </si>
+  <si>
+    <t>5-10 yr post PhD</t>
+  </si>
+  <si>
+    <t>michael.cowley@qut.edu.au</t>
+  </si>
+  <si>
+    <t>https://mjcowley.github.io</t>
+  </si>
+  <si>
+    <t>Cullan Howlett</t>
+  </si>
+  <si>
+    <t>c.howlett@uq.edu.au</t>
+  </si>
+  <si>
+    <t>Benjamin Roberts</t>
+  </si>
+  <si>
+    <t>Astroparticle</t>
+  </si>
+  <si>
+    <t>b.roberts@uq.edu.au</t>
+  </si>
+  <si>
+    <t>https://broberts.io/</t>
+  </si>
+  <si>
+    <t>Sarah Sweet</t>
+  </si>
+  <si>
+    <t>s.sweet@uq.edu.au</t>
+  </si>
+  <si>
+    <t>http://sarahsweet.com.au/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rossana Ruggeri </t>
+  </si>
+  <si>
+    <t>Lecturer</t>
+  </si>
+  <si>
+    <t>rossana.ruggeri@qut.edu.au</t>
+  </si>
+  <si>
+    <t>https://rossanaruggeri.github.io/</t>
+  </si>
+  <si>
+    <t>Belinda Nicholson</t>
+  </si>
+  <si>
+    <t>Research Fellow</t>
+  </si>
+  <si>
+    <t>Belinda.Nicholson@unisq.edu.au</t>
+  </si>
+  <si>
+    <t>Rebecca McElroy</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>rebecca.mcelroy@unisq.edu.au</t>
+  </si>
+  <si>
+    <t>https://rebeccamcelroy.github.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khaled Said </t>
+  </si>
+  <si>
+    <t>k.saidahmedsoliman@uq.edu.au</t>
+  </si>
+  <si>
+    <t>https://ksaid-1.github.io/Khaled-Said/</t>
+  </si>
+  <si>
+    <t>Gang Li</t>
+  </si>
+  <si>
+    <t>Postdoc</t>
+  </si>
+  <si>
+    <t>&lt;5 yr post PhD</t>
+  </si>
+  <si>
+    <t>Gang.Li@unisq.edu.au</t>
+  </si>
+  <si>
+    <t>https://ligangasteroseismic.github.io/index.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alexander Wallace </t>
+  </si>
+  <si>
+    <t>Alexander.Wallace@unisq.edu.au</t>
+  </si>
+  <si>
+    <t>Nandita Khetan</t>
+  </si>
+  <si>
+    <t>n.khetan@uq.edu.au</t>
+  </si>
+  <si>
+    <t>Simon Deeley</t>
+  </si>
+  <si>
+    <t>Research Assistant</t>
+  </si>
+  <si>
+    <t>s.deeley@uq.edu.au</t>
+  </si>
+  <si>
+    <t>Vanessa Porchet</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>PhD Student</t>
+  </si>
+  <si>
+    <t>in PhD</t>
+  </si>
+  <si>
+    <t>vanessajaehee.porchet@hdr.qut.edu.au</t>
+  </si>
+  <si>
+    <t>Lily Gustafson</t>
+  </si>
+  <si>
+    <t>lily.gustafson@hdr.qut.edu.au</t>
+  </si>
+  <si>
+    <t>Amber Tilly</t>
+  </si>
+  <si>
+    <t>Amber.Tilly@unisq.edu.au</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Duncan Wright</t>
-  </si>
-  <si>
-    <t>Duncan.Wright@unisq.edu.au</t>
-  </si>
-  <si>
-    <t>George Zhou</t>
-  </si>
-  <si>
-    <t>Associate Professor</t>
-  </si>
-  <si>
-    <t>george.zhou@unisq.edu.au</t>
-  </si>
-  <si>
-    <t>https://georgezhouastro.wordpress.com/</t>
-  </si>
-  <si>
-    <t>Chelsea Huang</t>
-  </si>
-  <si>
-    <t>chelsea.huang@unisq.edu.au</t>
-  </si>
-  <si>
-    <t>https://chelseahuangexoplanets.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simon Murphy </t>
-  </si>
-  <si>
-    <t>Springfield</t>
-  </si>
-  <si>
-    <t>Stars</t>
-  </si>
-  <si>
-    <t>Simon.Murphy@unisq.edu.au</t>
-  </si>
-  <si>
-    <t>https://simonjmurphy.github.io/</t>
-  </si>
-  <si>
-    <t>Holger Baumgardt</t>
-  </si>
-  <si>
-    <t>h.baumgardt@uq.edu.au</t>
-  </si>
-  <si>
-    <t>https://people.smp.uq.edu.au/HolgerBaumgardt/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Cowley </t>
-  </si>
-  <si>
-    <t>QUT</t>
-  </si>
-  <si>
-    <t>Senior Lecturer</t>
-  </si>
-  <si>
-    <t>Galaxies</t>
-  </si>
-  <si>
-    <t>5-10 yr post PhD</t>
-  </si>
-  <si>
-    <t>michael.cowley@qut.edu.au</t>
-  </si>
-  <si>
-    <t>https://mjcowley.github.io</t>
-  </si>
-  <si>
-    <t>Cullan Howlett</t>
-  </si>
-  <si>
-    <t>c.howlett@uq.edu.au</t>
-  </si>
-  <si>
-    <t>Benjamin Roberts</t>
-  </si>
-  <si>
-    <t>Astroparticle</t>
-  </si>
-  <si>
-    <t>b.roberts@uq.edu.au</t>
-  </si>
-  <si>
-    <t>https://broberts.io/</t>
-  </si>
-  <si>
-    <t>Sarah Sweet</t>
-  </si>
-  <si>
-    <t>s.sweet@uq.edu.au</t>
-  </si>
-  <si>
-    <t>http://sarahsweet.com.au/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rossana Ruggeri </t>
-  </si>
-  <si>
-    <t>Lecturer</t>
-  </si>
-  <si>
-    <t>rossana.ruggeri@qut.edu.au</t>
-  </si>
-  <si>
-    <t>https://rossanaruggeri.github.io/</t>
-  </si>
-  <si>
-    <t>Belinda Nicholson</t>
-  </si>
-  <si>
-    <t>Research Fellow</t>
-  </si>
-  <si>
-    <t>Belinda.Nicholson@unisq.edu.au</t>
-  </si>
-  <si>
-    <t>Rebecca McElroy</t>
-  </si>
-  <si>
-    <t>Remote</t>
-  </si>
-  <si>
-    <t>rebecca.mcelroy@unisq.edu.au</t>
-  </si>
-  <si>
-    <t>https://rebeccamcelroy.github.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khaled Said </t>
-  </si>
-  <si>
-    <t>k.saidahmedsoliman@uq.edu.au</t>
-  </si>
-  <si>
-    <t>https://ksaid-1.github.io/Khaled-Said/</t>
-  </si>
-  <si>
-    <t>Gang Li</t>
-  </si>
-  <si>
-    <t>Postdoc</t>
-  </si>
-  <si>
-    <t>&lt;5 yr post PhD</t>
-  </si>
-  <si>
-    <t>Gang.Li@unisq.edu.au</t>
-  </si>
-  <si>
-    <t>https://ligangasteroseismic.github.io/index.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alexander Wallace </t>
-  </si>
-  <si>
-    <t>Alexander.Wallace@unisq.edu.au</t>
-  </si>
-  <si>
-    <t>Nandita Khetan</t>
-  </si>
-  <si>
-    <t>n.khetan@uq.edu.au</t>
-  </si>
-  <si>
-    <t>Simon Deeley</t>
-  </si>
-  <si>
-    <t>Research Assistant</t>
-  </si>
-  <si>
-    <t>s.deeley@uq.edu.au</t>
-  </si>
-  <si>
-    <t>Vanessa Porchet</t>
-  </si>
-  <si>
-    <t>Student</t>
-  </si>
-  <si>
-    <t>PhD Student</t>
-  </si>
-  <si>
-    <t>in PhD</t>
-  </si>
-  <si>
-    <t>vanessajaehee.porchet@hdr.qut.edu.au</t>
-  </si>
-  <si>
-    <t>Lily Gustafson</t>
-  </si>
-  <si>
-    <t>lily.gustafson@hdr.qut.edu.au</t>
-  </si>
-  <si>
-    <t>Amber Tilly</t>
-  </si>
-  <si>
-    <t>Amber.Tilly@unisq.edu.au</t>
-  </si>
-  <si>
     <t>Anuj Gautam</t>
   </si>
   <si>
@@ -353,6 +353,9 @@
   </si>
   <si>
     <t>l.hobart@uq.edu.au</t>
+  </si>
+  <si>
+    <t>https://lachlanhobart.github.io/</t>
   </si>
   <si>
     <t>Narise Williams</t>
@@ -512,7 +515,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -526,10 +529,13 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -847,10 +853,10 @@
     <col min="5" max="5" style="7" width="19.433571428571426" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="7" width="19.290714285714284" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="7" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="22.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="39.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="39.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="22.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="39.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="8" width="39.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="22.5">
@@ -980,14 +986,12 @@
       <c r="I4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="5" t="s">
-        <v>30</v>
-      </c>
+      <c r="J4" s="4"/>
       <c r="K4" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>21</v>
@@ -1011,14 +1015,14 @@
         <v>24</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>21</v>
@@ -1030,7 +1034,7 @@
         <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>28</v>
@@ -1042,16 +1046,16 @@
         <v>24</v>
       </c>
       <c r="I6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="K6" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>21</v>
@@ -1063,7 +1067,7 @@
         <v>14</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>28</v>
@@ -1075,31 +1079,31 @@
         <v>18</v>
       </c>
       <c r="I7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>39</v>
       </c>
       <c r="K7" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>17</v>
@@ -1108,16 +1112,16 @@
         <v>24</v>
       </c>
       <c r="I8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="K8" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -1129,10 +1133,10 @@
         <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>17</v>
@@ -1141,19 +1145,19 @@
         <v>24</v>
       </c>
       <c r="I9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="K9" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>13</v>
@@ -1162,28 +1166,28 @@
         <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>53</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="K10" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1195,7 +1199,7 @@
         <v>14</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>16</v>
@@ -1207,14 +1211,14 @@
         <v>24</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1226,43 +1230,43 @@
         <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I12" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J12" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="K12" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>17</v>
@@ -1271,19 +1275,19 @@
         <v>18</v>
       </c>
       <c r="I13" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J13" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="K13" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>13</v>
@@ -1292,28 +1296,28 @@
         <v>14</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I14" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J14" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="K14" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>21</v>
@@ -1325,59 +1329,59 @@
         <v>14</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J16" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="K16" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1389,61 +1393,61 @@
         <v>14</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I17" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J17" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="K17" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I18" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="J18" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="K18" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>21</v>
@@ -1455,57 +1459,57 @@
         <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J19" s="4"/>
       <c r="K19" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J20" s="4"/>
       <c r="K20" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1517,88 +1521,88 @@
         <v>14</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J22" s="4"/>
       <c r="K22" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J23" s="4"/>
       <c r="K23" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>21</v>
@@ -1607,24 +1611,26 @@
         <v>22</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I24" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J24" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="J24" s="4"/>
       <c r="K24" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
@@ -1638,16 +1644,16 @@
         <v>22</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>24</v>
@@ -1667,16 +1673,16 @@
         <v>22</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>24</v>
@@ -1696,16 +1702,16 @@
         <v>22</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>24</v>
@@ -1722,19 +1728,19 @@
         <v>21</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>24</v>
@@ -1754,16 +1760,16 @@
         <v>22</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>18</v>
@@ -1780,19 +1786,19 @@
         <v>21</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>24</v>
@@ -1812,16 +1818,16 @@
         <v>13</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>18</v>
@@ -1841,16 +1847,16 @@
         <v>13</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>24</v>
@@ -1858,7 +1864,7 @@
       <c r="I32" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="J32" s="6" t="s">
+      <c r="J32" s="5" t="s">
         <v>108</v>
       </c>
       <c r="K32" s="3"/>
@@ -1874,16 +1880,16 @@
         <v>13</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="F33" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>24</v>
@@ -1905,16 +1911,16 @@
         <v>13</v>
       </c>
       <c r="D34" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="F34" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>24</v>
@@ -1922,12 +1928,14 @@
       <c r="I34" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="J34" s="4"/>
+      <c r="J34" s="4" t="s">
+        <v>113</v>
+      </c>
       <c r="K34" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="22.5">
       <c r="A35" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>12</v>
@@ -1936,29 +1944,29 @@
         <v>13</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="F35" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J35" s="4"/>
       <c r="K35" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="22.5">
       <c r="A36" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>12</v>
@@ -1967,29 +1975,29 @@
         <v>13</v>
       </c>
       <c r="D36" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="F36" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J36" s="4"/>
       <c r="K36" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="22.5">
       <c r="A37" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>12</v>
@@ -1998,29 +2006,29 @@
         <v>13</v>
       </c>
       <c r="D37" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="F37" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J37" s="4"/>
       <c r="K37" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="22.5">
       <c r="A38" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>12</v>
@@ -2029,29 +2037,29 @@
         <v>13</v>
       </c>
       <c r="D38" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="F38" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J38" s="4"/>
       <c r="K38" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="22.5">
       <c r="A39" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>12</v>
@@ -2060,29 +2068,29 @@
         <v>13</v>
       </c>
       <c r="D39" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J39" s="4"/>
       <c r="K39" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="22.5">
       <c r="A40" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>12</v>
@@ -2091,29 +2099,29 @@
         <v>13</v>
       </c>
       <c r="D40" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="22.5">
       <c r="A41" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>12</v>
@@ -2122,29 +2130,29 @@
         <v>13</v>
       </c>
       <c r="D41" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J41" s="4"/>
       <c r="K41" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="22.5">
       <c r="A42" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>12</v>
@@ -2153,31 +2161,31 @@
         <v>13</v>
       </c>
       <c r="D42" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="J42" s="6" t="s">
         <v>129</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>130</v>
       </c>
       <c r="K42" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="22.5">
       <c r="A43" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>12</v>
@@ -2186,29 +2194,29 @@
         <v>13</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J43" s="4"/>
       <c r="K43" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="22.5">
       <c r="A44" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>12</v>
@@ -2217,29 +2225,29 @@
         <v>13</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J44" s="4"/>
       <c r="K44" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="22.5">
       <c r="A45" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>12</v>
@@ -2248,31 +2256,31 @@
         <v>13</v>
       </c>
       <c r="D45" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="F45" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K45" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="22.5">
       <c r="A46" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>12</v>
@@ -2281,84 +2289,84 @@
         <v>13</v>
       </c>
       <c r="D46" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J46" s="4"/>
       <c r="K46" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="22.5">
       <c r="A47" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J47" s="4"/>
       <c r="K47" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="22.5">
       <c r="A48" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J48" s="4"/>
       <c r="K48" s="3"/>
